--- a/分省数据看板（月度）/趋势分析/26年5月.xlsx
+++ b/分省数据看板（月度）/趋势分析/26年5月.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>名称</t>
   </si>
   <si>
     <t>活跃用户</t>
+  </si>
+  <si>
+    <t>新用户</t>
   </si>
   <si>
     <t>营收</t>
@@ -160,16 +163,9 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -514,27 +510,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -655,133 +636,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -789,17 +770,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1112,709 +1093,814 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="5" max="5" width="16"/>
+    <col min="6" max="6" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1">
         <v>9984</v>
       </c>
       <c r="C2" s="1">
+        <v>3350</v>
+      </c>
+      <c r="D2" s="2">
         <v>56156</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="2">
         <v>7448</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="3">
         <v>5.62459935897436</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="4">
         <v>0.74599358974359</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1">
         <v>9065</v>
       </c>
       <c r="C3" s="1">
+        <v>2878</v>
+      </c>
+      <c r="D3" s="2">
         <v>37971</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="2">
         <v>6916</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="3">
         <v>4.18874793160507</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="4">
         <v>0.762934362934363</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1">
         <v>10565</v>
       </c>
       <c r="C4" s="1">
+        <v>4951</v>
+      </c>
+      <c r="D4" s="2">
         <v>24698</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="2">
         <v>7515</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="3">
         <v>2.33771888310459</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="4">
         <v>0.71131093232371</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
         <v>8018</v>
       </c>
       <c r="C5" s="1">
+        <v>6106</v>
+      </c>
+      <c r="D5" s="2">
         <v>9018</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="2">
         <v>6520</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="3">
         <v>1.12471938139187</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="4">
         <v>0.813170366674981</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1">
         <v>4864</v>
       </c>
       <c r="C6" s="1">
+        <v>2314</v>
+      </c>
+      <c r="D6" s="2">
         <v>13935</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="2">
         <v>3466</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="3">
         <v>2.86492598684211</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="4">
         <v>0.712582236842105</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1">
         <v>14725</v>
       </c>
       <c r="C7" s="1">
+        <v>4600</v>
+      </c>
+      <c r="D7" s="2">
         <v>70262</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="2">
         <v>11355</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="3">
         <v>4.77161290322581</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="4">
         <v>0.771137521222411</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1">
         <v>4593</v>
       </c>
       <c r="C8" s="1">
+        <v>1652</v>
+      </c>
+      <c r="D8" s="2">
         <v>18628</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="2">
         <v>3377</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="3">
         <v>4.05573699107337</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="4">
         <v>0.735249292401481</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1">
         <v>8449</v>
       </c>
       <c r="C9" s="1">
+        <v>2864</v>
+      </c>
+      <c r="D9" s="2">
         <v>26960</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="2">
         <v>6329</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="3">
         <v>3.19091016688365</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="4">
         <v>0.749082731684223</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1">
         <v>4421</v>
       </c>
       <c r="C10" s="1">
+        <v>1497</v>
+      </c>
+      <c r="D10" s="2">
         <v>27987</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="2">
         <v>3150</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="3">
         <v>6.33046821985976</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="4">
         <v>0.712508482243836</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1">
         <v>26787</v>
       </c>
       <c r="C11" s="1">
+        <v>10016</v>
+      </c>
+      <c r="D11" s="2">
         <v>156993</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="2">
         <v>19964</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="3">
         <v>5.86079068204726</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="4">
         <v>0.745286892895808</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12">
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="1">
         <v>8275</v>
       </c>
       <c r="C12" s="1">
+        <v>3166</v>
+      </c>
+      <c r="D12" s="2">
         <v>31599</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="2">
         <v>5916</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="3">
         <v>3.81861027190332</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="4">
         <v>0.714924471299094</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
+    <row r="13" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1">
         <v>14046</v>
       </c>
       <c r="C13" s="1">
+        <v>5125</v>
+      </c>
+      <c r="D13" s="2">
         <v>50871</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="2">
         <v>10049</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="3">
         <v>3.62174284493806</v>
       </c>
-      <c r="F13" s="3">
+      <c r="G13" s="4">
         <v>0.715434999288054</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
+    <row r="14" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1">
         <v>12779</v>
       </c>
       <c r="C14" s="1">
+        <v>4659</v>
+      </c>
+      <c r="D14" s="2">
         <v>44551</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="2">
         <v>9331</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="3">
         <v>3.48626653102747</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="4">
         <v>0.730182330385789</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15">
+    <row r="15" spans="1:7">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="1">
         <v>8961</v>
       </c>
       <c r="C15" s="1">
+        <v>3805</v>
+      </c>
+      <c r="D15" s="2">
         <v>19307</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="2">
         <v>6409</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="3">
         <v>2.15455864300859</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="4">
         <v>0.715210355987055</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16">
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1">
         <v>33770</v>
       </c>
       <c r="C16" s="1">
+        <v>12060</v>
+      </c>
+      <c r="D16" s="2">
         <v>94944</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="2">
         <v>25613</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="3">
         <v>2.81148948771099</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="4">
         <v>0.758454249333728</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17">
+    <row r="17" spans="1:7">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1">
         <v>12256</v>
       </c>
       <c r="C17" s="1">
+        <v>6059</v>
+      </c>
+      <c r="D17" s="2">
         <v>19747</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="2">
         <v>8537</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="3">
         <v>1.61121083550914</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="4">
         <v>0.696556788511749</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18">
+    <row r="18" spans="1:7">
+      <c r="A18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1">
         <v>9437</v>
       </c>
       <c r="C18" s="1">
+        <v>4069</v>
+      </c>
+      <c r="D18" s="2">
         <v>29458</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="2">
         <v>6930</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="3">
         <v>3.12154286319805</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="4">
         <v>0.734343541379676</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19">
+    <row r="19" spans="1:7">
+      <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1">
         <v>11582</v>
       </c>
       <c r="C19" s="1">
+        <v>4949</v>
+      </c>
+      <c r="D19" s="2">
         <v>40519</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="2">
         <v>8430</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="3">
         <v>3.49844586427215</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="4">
         <v>0.727853565878087</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20">
+    <row r="20" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="1">
         <v>22493</v>
       </c>
       <c r="C20" s="1">
+        <v>9611</v>
+      </c>
+      <c r="D20" s="2">
         <v>101658</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="2">
         <v>16147</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="3">
         <v>4.51953941226159</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="4">
         <v>0.717867781087449</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21">
+    <row r="21" spans="1:7">
+      <c r="A21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1">
         <v>4158</v>
       </c>
       <c r="C21" s="1">
+        <v>1973</v>
+      </c>
+      <c r="D21" s="2">
         <v>8864</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="2">
         <v>2936</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="3">
         <v>2.13179413179413</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="4">
         <v>0.706108706108706</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22">
+    <row r="22" spans="1:7">
+      <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="1">
         <v>2456</v>
       </c>
       <c r="C22" s="1">
+        <v>1107</v>
+      </c>
+      <c r="D22" s="2">
         <v>9057</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="2">
         <v>1771</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="3">
         <v>3.68770358306189</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="4">
         <v>0.721091205211726</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23">
+    <row r="23" spans="1:7">
+      <c r="A23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1">
         <v>6680</v>
       </c>
       <c r="C23" s="1">
+        <v>2686</v>
+      </c>
+      <c r="D23" s="2">
         <v>28358</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="2">
         <v>4813</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F23" s="3">
         <v>4.24520958083832</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="4">
         <v>0.720508982035928</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:7">
+      <c r="A24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1">
+        <v>9926</v>
+      </c>
+      <c r="C24" s="1">
+        <v>4337</v>
+      </c>
+      <c r="D24" s="2">
+        <v>32922</v>
+      </c>
+      <c r="E24" s="2">
+        <v>7308</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3.31674390489623</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0.736248236953456</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3500</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1754</v>
+      </c>
+      <c r="D25" s="2">
+        <v>7632</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2379</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2.18057142857143</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0.679714285714286</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4154</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2050</v>
+      </c>
+      <c r="D26" s="2">
+        <v>15415</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2731</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3.71088107847857</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0.657438613384689</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="1">
+        <v>263</v>
+      </c>
+      <c r="C27" s="1">
+        <v>119</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1660</v>
+      </c>
+      <c r="E27" s="2">
+        <v>171</v>
+      </c>
+      <c r="F27" s="3">
+        <v>6.31178707224335</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0.650190114068441</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="1">
+        <v>6338</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3394</v>
+      </c>
+      <c r="D28" s="2">
+        <v>14305</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4525</v>
+      </c>
+      <c r="F28" s="3">
+        <v>2.25702114231619</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0.713947617544967</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1">
+        <v>3749</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1774</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5312</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2520</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1.41691117631368</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0.672179247799413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1092</v>
+      </c>
+      <c r="C30" s="1">
+        <v>507</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4519</v>
+      </c>
+      <c r="E30" s="2">
+        <v>803</v>
+      </c>
+      <c r="F30" s="3">
+        <v>4.13827838827839</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0.735347985347985</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2088</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1146</v>
+      </c>
+      <c r="D31" s="2">
+        <v>4839</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1590</v>
+      </c>
+      <c r="F31" s="3">
+        <v>2.31752873563218</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0.761494252873563</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4182</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1898</v>
+      </c>
+      <c r="D32" s="2">
+        <v>9485</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2782</v>
+      </c>
+      <c r="F32" s="3">
+        <v>2.26805356288857</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0.665231946437111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="1">
+        <v>34</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4</v>
+      </c>
+      <c r="D33" s="2">
+        <v>317</v>
+      </c>
+      <c r="E33" s="2">
         <v>28</v>
       </c>
-      <c r="B24">
-        <v>9926</v>
-      </c>
-      <c r="C24" s="1">
-        <v>32922</v>
-      </c>
-      <c r="D24" s="1">
-        <v>7308</v>
-      </c>
-      <c r="E24" s="2">
-        <v>3.31674390489623</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0.736248236953456</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25">
-        <v>3500</v>
-      </c>
-      <c r="C25" s="1">
-        <v>7632</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2379</v>
-      </c>
-      <c r="E25" s="2">
-        <v>2.18057142857143</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0.679714285714286</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26">
-        <v>4154</v>
-      </c>
-      <c r="C26" s="1">
-        <v>15415</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2731</v>
-      </c>
-      <c r="E26" s="2">
-        <v>3.71088107847857</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0.657438613384689</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27">
-        <v>263</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1660</v>
-      </c>
-      <c r="D27" s="1">
-        <v>171</v>
-      </c>
-      <c r="E27" s="2">
-        <v>6.31178707224335</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0.650190114068441</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28">
-        <v>6338</v>
-      </c>
-      <c r="C28" s="1">
-        <v>14305</v>
-      </c>
-      <c r="D28" s="1">
-        <v>4525</v>
-      </c>
-      <c r="E28" s="2">
-        <v>2.25702114231619</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0.713947617544967</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29">
-        <v>3749</v>
-      </c>
-      <c r="C29" s="1">
-        <v>5312</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2520</v>
-      </c>
-      <c r="E29" s="2">
-        <v>1.41691117631368</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0.672179247799413</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30">
-        <v>1092</v>
-      </c>
-      <c r="C30" s="1">
-        <v>4519</v>
-      </c>
-      <c r="D30" s="1">
-        <v>803</v>
-      </c>
-      <c r="E30" s="2">
-        <v>4.13827838827839</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0.735347985347985</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31">
-        <v>2088</v>
-      </c>
-      <c r="C31" s="1">
-        <v>4839</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1590</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2.31752873563218</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0.761494252873563</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32">
-        <v>4182</v>
-      </c>
-      <c r="C32" s="1">
-        <v>9485</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2782</v>
-      </c>
-      <c r="E32" s="2">
-        <v>2.26805356288857</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0.665231946437111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33">
-        <v>34</v>
-      </c>
-      <c r="C33" s="1">
-        <v>317</v>
-      </c>
-      <c r="D33" s="1">
-        <v>28</v>
-      </c>
-      <c r="E33" s="2">
+      <c r="F33" s="3">
         <v>9.32352941176471</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="4">
         <v>0.823529411764706</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34">
+    <row r="34" spans="1:7">
+      <c r="A34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="1">
         <v>4</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
         <v>2</v>
       </c>
-      <c r="E34" s="2">
+      <c r="F34" s="3">
         <v>0</v>
       </c>
-      <c r="F34" s="3">
+      <c r="G34" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35">
+    <row r="35" spans="1:7">
+      <c r="A35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="1">
         <v>9</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
         <v>0</v>
       </c>
-      <c r="D35" s="4">
+      <c r="E35" s="2">
         <v>6</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F35" s="3">
         <v>0</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="4">
         <v>0.666666666666667</v>
       </c>
     </row>
